--- a/outputs/daily/hr_rankings_2026-10-27.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-27.xlsx
@@ -735,24 +735,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -765,14 +765,26 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.4</v>
+        <v>54.8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -786,26 +798,26 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>61.9</v>
+        <v>59.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>37.8</v>
+        <v>16.6</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -819,7 +831,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -844,7 +856,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -866,100 +878,124 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.2549</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+          <t>0.2018</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -975,24 +1011,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -1005,14 +1041,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>53.3</v>
+        <v>54.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1030,7 +1066,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>59.6</v>
+        <v>61.9</v>
       </c>
       <c r="Q3" t="n">
         <v>41.2</v>
@@ -1039,13 +1075,13 @@
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>60</v>
       </c>
       <c r="U3" t="n">
-        <v>16.6</v>
+        <v>37.8</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1059,7 +1095,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1106,17 +1142,17 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1126,72 +1162,72 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.2549</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr"/>
@@ -1248,11 +1284,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>51.6</v>
+        <v>50.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1273,7 +1321,7 @@
         <v>50.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R4" t="n">
         <v>27.6</v>
@@ -1282,7 +1330,7 @@
         <v>88.7</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
         <v>63.3</v>
@@ -1324,7 +1372,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1361,7 +1409,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1434,12 +1482,36 @@
           <t>0.1951</t>
         </is>
       </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
@@ -1455,24 +1527,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -1485,14 +1557,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>47.1</v>
+        <v>47.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1506,26 +1590,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>43.3</v>
+        <v>36.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R5" t="n">
         <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>65.2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1539,7 +1623,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1564,7 +1648,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1581,27 +1665,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1611,75 +1695,99 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1288</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+          <t>0.1715</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
@@ -1695,12 +1803,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1725,14 +1833,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>47.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1746,26 +1866,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.5</v>
+        <v>38.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>37.8</v>
+        <v>25.3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1779,7 +1899,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1804,7 +1924,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1821,7 +1941,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1836,12 +1956,12 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1851,75 +1971,99 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1446</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+          <t>0.1565</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -1935,24 +2079,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -1965,14 +2109,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>47.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1986,26 +2142,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>47.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R7" t="n">
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>71.7</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>13.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2019,7 +2175,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2044,7 +2200,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2061,12 +2217,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2076,90 +2232,114 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1342</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
@@ -2175,24 +2355,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -2205,14 +2385,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>46.2</v>
+        <v>47.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2230,7 +2410,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>38.2</v>
+        <v>43.3</v>
       </c>
       <c r="Q8" t="n">
         <v>41.2</v>
@@ -2239,13 +2419,13 @@
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T8" t="n">
         <v>60</v>
       </c>
       <c r="U8" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2259,7 +2439,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2301,22 +2481,22 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2331,67 +2511,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr"/>
@@ -2415,24 +2595,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -2445,14 +2625,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>46.2</v>
+        <v>46.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2466,11 +2646,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36.6</v>
+        <v>41</v>
       </c>
       <c r="Q9" t="n">
         <v>41.2</v>
@@ -2479,13 +2659,13 @@
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
       </c>
       <c r="U9" t="n">
-        <v>65.2</v>
+        <v>20.9</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2499,7 +2679,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2541,22 +2721,22 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2571,67 +2751,67 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr"/>
@@ -2655,12 +2835,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2685,14 +2865,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2706,26 +2898,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>47.1</v>
+        <v>39.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R10" t="n">
         <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>13.3</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -2739,7 +2931,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -2764,7 +2956,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -2781,7 +2973,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2791,95 +2983,119 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1342</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
@@ -3855,12 +4071,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3885,14 +4101,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>32.5</v>
+        <v>31.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3906,26 +4134,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -3939,7 +4167,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3964,7 +4192,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -3981,12 +4209,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -3996,12 +4224,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4011,75 +4239,99 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+          <t>0.1042</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -4095,24 +4347,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -4125,12 +4377,24 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
         <v>31.3</v>
       </c>
@@ -4150,22 +4414,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>12.8</v>
+        <v>10.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>18.3</v>
+        <v>24.9</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4179,7 +4443,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4204,7 +4468,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4221,27 +4485,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4251,75 +4515,99 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1186</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
@@ -4335,24 +4623,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -4365,14 +4653,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>29.9</v>
+        <v>31.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4390,7 +4678,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11.1</v>
+        <v>12.8</v>
       </c>
       <c r="Q17" t="n">
         <v>41.2</v>
@@ -4399,13 +4687,13 @@
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T17" t="n">
         <v>60</v>
       </c>
       <c r="U17" t="n">
-        <v>23.7</v>
+        <v>18.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4419,7 +4707,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -4461,22 +4749,22 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -4491,67 +4779,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr"/>
@@ -4575,24 +4863,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -4605,14 +4893,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>29.4</v>
+        <v>30.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4630,22 +4930,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T18" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>27</v>
+        <v>17.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -4659,7 +4959,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -4684,7 +4984,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -4701,12 +5001,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -4716,12 +5016,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -4731,75 +5031,99 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0829</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+          <t>0.0974</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -4815,24 +5139,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -4845,14 +5169,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>28.8</v>
+        <v>29.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -4866,26 +5190,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>41.2</v>
+        <v>40.2</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>17.3</v>
+        <v>27</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -4899,7 +5223,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -4941,12 +5265,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -4956,12 +5280,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -4971,67 +5295,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr"/>
@@ -5381,24 +5705,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -5411,14 +5735,26 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.4</v>
+        <v>54.8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5432,26 +5768,26 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>61.9</v>
+        <v>59.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>37.8</v>
+        <v>16.6</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -5465,7 +5801,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -5490,7 +5826,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -5512,100 +5848,124 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.2549</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+          <t>0.2018</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -5621,24 +5981,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -5651,14 +6011,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>53.3</v>
+        <v>54.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5676,7 +6036,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>59.6</v>
+        <v>61.9</v>
       </c>
       <c r="Q3" t="n">
         <v>41.2</v>
@@ -5685,13 +6045,13 @@
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>60</v>
       </c>
       <c r="U3" t="n">
-        <v>16.6</v>
+        <v>37.8</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -5705,7 +6065,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -5752,17 +6112,17 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -5772,72 +6132,72 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.2549</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr"/>
@@ -5894,11 +6254,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>51.6</v>
+        <v>50.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -5919,7 +6291,7 @@
         <v>50.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R4" t="n">
         <v>27.6</v>
@@ -5928,7 +6300,7 @@
         <v>88.7</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
         <v>63.3</v>
@@ -5970,7 +6342,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -6007,7 +6379,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -6080,12 +6452,36 @@
           <t>0.1951</t>
         </is>
       </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
@@ -6101,24 +6497,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -6131,14 +6527,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>47.1</v>
+        <v>47.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6152,26 +6560,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>43.3</v>
+        <v>36.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R5" t="n">
         <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>65.2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -6185,7 +6593,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -6210,7 +6618,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -6227,27 +6635,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -6257,75 +6665,99 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1288</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+          <t>0.1715</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
@@ -6341,12 +6773,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6371,14 +6803,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>47.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6392,26 +6836,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.5</v>
+        <v>38.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>37.8</v>
+        <v>25.3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -6425,7 +6869,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -6450,7 +6894,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -6467,7 +6911,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -6482,12 +6926,12 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -6497,75 +6941,99 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1446</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+          <t>0.1565</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -6581,24 +7049,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -6611,14 +7079,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>47.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -6632,26 +7112,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>47.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R7" t="n">
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>71.7</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>13.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -6665,7 +7145,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -6690,7 +7170,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -6707,12 +7187,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -6722,90 +7202,114 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1342</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
@@ -6821,24 +7325,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -6851,14 +7355,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>46.2</v>
+        <v>47.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -6876,7 +7380,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>38.2</v>
+        <v>43.3</v>
       </c>
       <c r="Q8" t="n">
         <v>41.2</v>
@@ -6885,13 +7389,13 @@
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T8" t="n">
         <v>60</v>
       </c>
       <c r="U8" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -6905,7 +7409,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -6947,22 +7451,22 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -6977,67 +7481,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr"/>
@@ -7061,24 +7565,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -7091,14 +7595,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>46.2</v>
+        <v>46.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -7112,11 +7616,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36.6</v>
+        <v>41</v>
       </c>
       <c r="Q9" t="n">
         <v>41.2</v>
@@ -7125,13 +7629,13 @@
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
       </c>
       <c r="U9" t="n">
-        <v>65.2</v>
+        <v>20.9</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -7145,7 +7649,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -7187,22 +7691,22 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -7217,67 +7721,67 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr"/>
@@ -7301,12 +7805,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -7331,14 +7835,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -7352,26 +7868,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>47.1</v>
+        <v>39.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R10" t="n">
         <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>13.3</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -7385,7 +7901,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -7410,7 +7926,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -7427,7 +7943,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -7437,95 +7953,119 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1342</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
@@ -8501,12 +9041,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -8531,14 +9071,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>32.5</v>
+        <v>31.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -8552,26 +9104,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -8585,7 +9137,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -8610,7 +9162,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -8627,12 +9179,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -8642,12 +9194,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -8657,75 +9209,99 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+          <t>0.1042</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -8741,24 +9317,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -8771,12 +9347,24 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
         <v>31.3</v>
       </c>
@@ -8796,22 +9384,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>12.8</v>
+        <v>10.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>18.3</v>
+        <v>24.9</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -8825,7 +9413,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -8850,7 +9438,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -8867,27 +9455,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -8897,75 +9485,99 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1186</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
@@ -8981,24 +9593,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -9011,14 +9623,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>29.9</v>
+        <v>31.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9036,7 +9648,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11.1</v>
+        <v>12.8</v>
       </c>
       <c r="Q17" t="n">
         <v>41.2</v>
@@ -9045,13 +9657,13 @@
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T17" t="n">
         <v>60</v>
       </c>
       <c r="U17" t="n">
-        <v>23.7</v>
+        <v>18.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -9065,7 +9677,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -9107,22 +9719,22 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -9137,67 +9749,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr"/>
@@ -9221,24 +9833,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -9251,14 +9863,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>29.4</v>
+        <v>30.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -9276,22 +9900,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T18" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>27</v>
+        <v>17.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -9305,7 +9929,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -9330,7 +9954,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -9347,12 +9971,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -9362,12 +9986,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -9377,75 +10001,99 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0829</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+          <t>0.0974</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -9461,24 +10109,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -9491,14 +10139,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>28.8</v>
+        <v>29.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -9512,26 +10160,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>41.2</v>
+        <v>40.2</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>17.3</v>
+        <v>27</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -9545,7 +10193,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -9587,12 +10235,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -9602,12 +10250,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -9617,67 +10265,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-10-27.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-27.xlsx
@@ -735,24 +735,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -765,26 +765,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,26 +786,26 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>59.6</v>
+        <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U2" t="n">
-        <v>16.6</v>
+        <v>37.8</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -826,24 +814,24 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -856,7 +844,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -878,124 +866,100 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.2018</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.2549</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -1011,24 +975,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -1041,14 +1005,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1062,26 +1038,26 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>61.9</v>
+        <v>59.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R3" t="n">
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>37.8</v>
+        <v>16.6</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1090,24 +1066,24 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -1120,7 +1096,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -1142,100 +1118,124 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.2549</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+          <t>0.2018</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1527,24 +1527,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -1557,26 +1557,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>47.8</v>
+        <v>50.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1590,26 +1578,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>36.6</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R5" t="n">
         <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U5" t="n">
-        <v>65.2</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1618,24 +1606,24 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -1648,7 +1636,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1665,27 +1653,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1695,99 +1683,75 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1715</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
@@ -1803,12 +1767,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1833,7 +1797,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1852,7 +1816,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.7</v>
+        <v>49.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1870,7 +1834,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>38.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
         <v>40.1</v>
@@ -1879,13 +1843,13 @@
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1894,12 +1858,12 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1941,22 +1905,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1971,67 +1935,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2109,7 +2073,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2128,7 +2092,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.2</v>
+        <v>48.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2155,7 +2119,7 @@
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2170,12 +2134,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2355,12 +2319,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2385,14 +2349,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>47.1</v>
+        <v>46.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2406,11 +2370,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q8" t="n">
         <v>41.2</v>
@@ -2419,13 +2383,13 @@
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>95.5</v>
+        <v>71.7</v>
       </c>
       <c r="T8" t="n">
         <v>60</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>54.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2434,12 +2398,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2481,22 +2445,22 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2511,67 +2475,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>32.39</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr"/>
@@ -2674,7 +2638,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -2926,7 +2890,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -3111,24 +3075,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -3141,12 +3105,24 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L11" t="n">
         <v>44.9</v>
       </c>
@@ -3162,26 +3138,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R11" t="n">
         <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>54.9</v>
+        <v>25.3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3190,24 +3166,24 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3220,7 +3196,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3237,12 +3213,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3252,12 +3228,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3267,75 +3243,99 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2134</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+          <t>0.1565</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3381,14 +3381,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>36.5</v>
+        <v>35.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3402,11 +3402,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
         <v>41.2</v>
@@ -3415,13 +3415,13 @@
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>60</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3430,12 +3430,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3477,22 +3477,22 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -3507,67 +3507,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr"/>
@@ -3591,12 +3591,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3621,14 +3621,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3642,11 +3642,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>11.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
         <v>41.2</v>
@@ -3655,13 +3655,13 @@
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T13" t="n">
         <v>60</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -3747,67 +3747,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr"/>
@@ -3831,24 +3831,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -3861,14 +3861,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>33.2</v>
+        <v>32.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3882,26 +3894,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.2</v>
+        <v>16.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>38.7</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>92.09999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>15.3</v>
+        <v>5.1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -3910,24 +3922,24 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3940,7 +3952,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -3957,12 +3969,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -3972,12 +3984,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -3987,75 +3999,99 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.079</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -4071,24 +4107,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -4101,26 +4137,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>31.4</v>
+        <v>32.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4134,26 +4158,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>11.1</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>23.7</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4162,24 +4186,24 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4192,7 +4216,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4214,7 +4238,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4224,12 +4248,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4239,99 +4263,75 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1042</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -4347,24 +4347,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -4377,26 +4377,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>31.3</v>
+        <v>31.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4414,22 +4402,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>10.5</v>
+        <v>0.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U16" t="n">
-        <v>24.9</v>
+        <v>15.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4438,24 +4426,24 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4468,7 +4456,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4490,7 +4478,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4500,12 +4488,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4515,99 +4503,75 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
@@ -4623,24 +4587,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -4653,14 +4617,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4674,26 +4650,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>12.8</v>
+        <v>11.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>18.3</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4702,24 +4678,24 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4732,7 +4708,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -4749,27 +4725,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -4779,75 +4755,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1186</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.1042</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.3</v>
+        <v>31.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4926,11 +4926,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q18" t="n">
         <v>40.1</v>
@@ -4939,13 +4939,13 @@
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>17.3</v>
+        <v>24.9</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -4954,24 +4954,24 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5001,12 +5001,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5031,67 +5031,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -5705,24 +5705,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -5735,26 +5735,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5768,26 +5756,26 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>59.6</v>
+        <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U2" t="n">
-        <v>16.6</v>
+        <v>37.8</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -5796,24 +5784,24 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -5826,7 +5814,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -5848,124 +5836,100 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.2018</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.2549</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -5981,24 +5945,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -6011,14 +5975,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6032,26 +6008,26 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>61.9</v>
+        <v>59.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R3" t="n">
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>37.8</v>
+        <v>16.6</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -6060,24 +6036,24 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -6090,7 +6066,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -6112,100 +6088,124 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.2549</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+          <t>0.2018</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -6497,24 +6497,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -6527,26 +6527,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>47.8</v>
+        <v>50.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6560,26 +6548,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>36.6</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R5" t="n">
         <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U5" t="n">
-        <v>65.2</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -6588,24 +6576,24 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -6618,7 +6606,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -6635,27 +6623,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -6665,99 +6653,75 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1715</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
@@ -6773,12 +6737,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6803,7 +6767,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -6822,7 +6786,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.7</v>
+        <v>49.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6840,7 +6804,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>38.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
         <v>40.1</v>
@@ -6849,13 +6813,13 @@
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -6864,12 +6828,12 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -6911,22 +6875,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -6941,67 +6905,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -7079,7 +7043,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7098,7 +7062,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.2</v>
+        <v>48.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7125,7 +7089,7 @@
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -7140,12 +7104,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7325,12 +7289,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7355,14 +7319,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>47.1</v>
+        <v>46.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7376,11 +7340,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q8" t="n">
         <v>41.2</v>
@@ -7389,13 +7353,13 @@
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>95.5</v>
+        <v>71.7</v>
       </c>
       <c r="T8" t="n">
         <v>60</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>54.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7404,12 +7368,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -7451,22 +7415,22 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -7481,67 +7445,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>32.39</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr"/>
@@ -7644,7 +7608,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -7896,7 +7860,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -8081,24 +8045,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -8111,12 +8075,24 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L11" t="n">
         <v>44.9</v>
       </c>
@@ -8132,26 +8108,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R11" t="n">
         <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>54.9</v>
+        <v>25.3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -8160,24 +8136,24 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8190,7 +8166,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -8207,12 +8183,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -8222,12 +8198,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8237,75 +8213,99 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2134</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+          <t>0.1565</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8351,14 +8351,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>36.5</v>
+        <v>35.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8372,11 +8372,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
         <v>41.2</v>
@@ -8385,13 +8385,13 @@
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>60</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -8400,12 +8400,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -8447,22 +8447,22 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -8477,67 +8477,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr"/>
@@ -8561,12 +8561,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -8591,14 +8591,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -8612,11 +8612,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>11.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
         <v>41.2</v>
@@ -8625,13 +8625,13 @@
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T13" t="n">
         <v>60</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -8640,12 +8640,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -8687,22 +8687,22 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -8717,67 +8717,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr"/>
@@ -8801,24 +8801,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -8831,14 +8831,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>33.2</v>
+        <v>32.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -8852,26 +8864,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.2</v>
+        <v>16.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>38.7</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>92.09999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>15.3</v>
+        <v>5.1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -8880,24 +8892,24 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8910,7 +8922,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -8927,12 +8939,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -8942,12 +8954,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -8957,75 +8969,99 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.079</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -9041,24 +9077,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -9071,26 +9107,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>31.4</v>
+        <v>32.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9104,26 +9128,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>11.1</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>23.7</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9132,24 +9156,24 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9162,7 +9186,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9184,7 +9208,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9194,12 +9218,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9209,99 +9233,75 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1042</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -9317,24 +9317,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -9347,26 +9347,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>31.3</v>
+        <v>31.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9384,22 +9372,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>10.5</v>
+        <v>0.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U16" t="n">
-        <v>24.9</v>
+        <v>15.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -9408,24 +9396,24 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9438,7 +9426,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -9460,7 +9448,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -9470,12 +9458,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -9485,99 +9473,75 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
@@ -9593,24 +9557,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -9623,14 +9587,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9644,26 +9620,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>12.8</v>
+        <v>11.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>18.3</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -9672,24 +9648,24 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9702,7 +9678,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -9719,27 +9695,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -9749,75 +9725,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1186</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.1042</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -9882,7 +9882,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.3</v>
+        <v>31.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -9896,11 +9896,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q18" t="n">
         <v>40.1</v>
@@ -9909,13 +9909,13 @@
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>17.3</v>
+        <v>24.9</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -9924,24 +9924,24 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -9971,12 +9971,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -9986,12 +9986,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10001,67 +10001,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
